--- a/Суббота.xlsx
+++ b/Суббота.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Desktop\Посещаемость\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Documents\Folder\Generator_rep_attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,10 +87,10 @@
     <t>Кинетов Жан Бахытович</t>
   </si>
   <si>
-    <t>Абдрахман Хасен Алпамысович</t>
-  </si>
-  <si>
     <t>С 9:45</t>
+  </si>
+  <si>
+    <t>Абдрахманов Хасен Алпамысович</t>
   </si>
 </sst>
 </file>
@@ -811,7 +811,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="5"/>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -835,7 +835,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="5"/>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -859,7 +859,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="5"/>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -883,7 +883,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="5"/>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -891,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7">
         <v>9433309</v>
@@ -907,7 +907,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="7"/>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
